--- a/daily_matches/job_matches_2026-03-31.xlsx
+++ b/daily_matches/job_matches_2026-03-31.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a09d1fbe2ac450</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4ecf995582c407</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Optimization</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4920d413c7cea7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Optimization</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51de31e2196d525</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Applied AI/ML - Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, Terraform, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=74636f4c4f775a6b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wisdom AI</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
+          <t>Data Scientist, Glue, Athena, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b281d8509a99096</t>
+          <t>https://www.indeed.com/viewjob?jk=fea87c0434300006</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,29 +661,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Glue, Athena, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82244848569b247</t>
+          <t>https://www.indeed.com/viewjob?jk=de12d872bb21a7f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,33 +692,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Redshift, Data Lake, Redshift, PostgreSQL, Tableau, Power BI, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb8fffe975697c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Vehicle Engineering</t>
+          <t>Applied AI/ML Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, AWS SageMaker, GCP Vertex AI, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,94 +741,94 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb6af4580805717</t>
+          <t>https://www.indeed.com/viewjob?jk=811fe59aac671796</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java / Angular Engineer (FTE/Onsite/USC/GC)</t>
+          <t>Backend Software Engineer II – Go (Golang)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MedBridge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R, Java</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3960985d2bb83a35</t>
+          <t>https://www.indeed.com/viewjob?jk=5def83b9fd728b8b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Xplor Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Copilot, CI/CD, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ed03eb48c65722</t>
+          <t>https://www.indeed.com/viewjob?jk=ec10cfe3d6cfba51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI &amp; Automation Engineer (Industry Placement – 6 Months)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Puzzle Metrics Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5482048561698a60</t>
+          <t>https://www.indeed.com/viewjob?jk=4dee69139258ee7f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Search Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Copilot, Git, Python, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffd4654729c4f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb435c09db16d9b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-31.xlsx
+++ b/daily_matches/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4ecf995582c407</t>
+          <t>https://www.indeed.com/viewjob?jk=62b1c6a1aa58e944</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Keras, Docker, Kubernetes, Jenkins, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=be94bd1e157aa7f4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, MLflow, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=212034a780eca72d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI/ML - Senior Associate</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Terraform, Kafka, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74636f4c4f775a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd070469cd6bdc5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Athena, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea87c0434300006</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Distinguished Applied Software Engineer, Ad Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Athena, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Kubernetes, Git, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de12d872bb21a7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c734aeef9e92336</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Scala, Bayesian</t>
+          <t>LangChain, LLaMA, Gemini, Mistral, Hugging Face, FAISS, Sentence Transformers, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb8fffe975697c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c847c543c78bdd0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied AI/ML Associate</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, AWS SageMaker, GCP Vertex AI, Git, Python, R, Optimization</t>
+          <t>EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811fe59aac671796</t>
+          <t>https://www.indeed.com/viewjob?jk=35e4e28761dc5442</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Software Engineer II – Go (Golang)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MedBridge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, MySQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5def83b9fd728b8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xplor Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec10cfe3d6cfba51</t>
+          <t>https://www.indeed.com/viewjob?jk=d965dc8c18c2f3fc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer (Industry Placement – 6 Months)</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Puzzle Metrics Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dee69139258ee7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfee97da6d6ebf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Search Engineering</t>
+          <t>Automation &amp; Digitalization Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gibsonton, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Python, R, Java, Scala, A/B Testing</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb435c09db16d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=cced9f9e48a0f11b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=625c543ecd59d740</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-31.xlsx
+++ b/daily_matches/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Arcadia.io</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, RAG, S3, Athena, Redshift, Jenkins, Git, Snowflake, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b1c6a1aa58e944</t>
+          <t>https://www.indeed.com/viewjob?jk=38dd209211574c60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Machine Learning Engineer, Recommendations (Experience)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Soundcloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Keras, Docker, Kubernetes, Jenkins, Tableau</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be94bd1e157aa7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca65a65f49d23cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, MLflow, CI/CD, Git, Databricks</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212034a780eca72d</t>
+          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Zone IT Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, FastAPI, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd070469cd6bdc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ea42244b00d22ed0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Hadoop</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9388b5ffd0ba0e6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Distinguished Applied Software Engineer, Ad Platforms</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Kubernetes, Git, R, Scala</t>
+          <t>S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c734aeef9e92336</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Gemini, Mistral, Hugging Face, FAISS, Sentence Transformers, Kubernetes, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c847c543c78bdd0</t>
+          <t>https://www.indeed.com/viewjob?jk=292934806b1fb645</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Kubernetes, Terraform, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e4e28761dc5442</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, Kafka, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8a29212b4b365c33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CBIZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, S3, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,112 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d965dc8c18c2f3fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfee97da6d6ebf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Automation &amp; Digitalization Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Gibsonton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cced9f9e48a0f11b</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Full-Stack AI Application Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=625c543ecd59d740</t>
+          <t>https://www.indeed.com/viewjob?jk=ebadd001a801356b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-31.xlsx
+++ b/daily_matches/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arcadia.io</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Athena, Redshift, Jenkins, Git, Snowflake, Redshift, Tableau</t>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, BigQuery, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dd209211574c60</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Recommendations (Experience)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Soundcloud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca65a65f49d23cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, NoSQL, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zone IT Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, FastAPI, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea42244b00d22ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9388b5ffd0ba0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5ec9a65a1c3c38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, EC2, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e56ee059c6d0ffc4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292934806b1fb645</t>
+          <t>https://www.indeed.com/viewjob?jk=1cdfc5c60054367a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Terraform, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, EC2, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=49f21c74d755f6da</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Agentic AI</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,1512 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a29212b4b365c33</t>
+          <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CBIZ</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b038e98910299c36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PySpark</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAP AI Business Services Consultant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, FastAPI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0716b79f18650b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, AWS SageMaker, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, FastAPI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19592463fd1167be</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Associate Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Premise Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, MLflow, CI/CD, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2afc92ff8833e19b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Premise Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b367254e6530d84</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SAP AI Business Services Consultant</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0b3720f78fa3e23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BWE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Synapse, Dataflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data and AI Platform</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, Jenkins, Git, Kafka, Hadoop, MySQL, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44812aa8e4e69e03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud Service Desk Analyst</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0813f70a2c811ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Junior DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CrowdStrike Cloud Security Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ce9baff658ab310</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Marketing Data Engineer (Digital Marketing Specialist)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Indiana University</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bloomington, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53f4525d522d376a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mid-Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AR Worx</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e728811cbcf41fd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a456d04ee6d4d6d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e3f619eb8606b64</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ca268e9ad4fd23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GCP Cloud Security Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Product Owner - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Oldcastle APG</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, Data Lake, Snowflake, Databricks, Redshift, Tableau, Power BI, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b20ece8e992c70a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, AWS SageMaker, S3, Redshift, MLflow, Redshift, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b14866eeb0277e</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa09609f5402dd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, AI Security Platform</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BeyondTrust</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc3e989faec2f82e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Docker, Kubernetes, CI/CD, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db2277d86f675cd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=636019655617d575</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test - AI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Delos Data</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48ac984c15b618c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rula</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b52b97c567c9622</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BWE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5224353dd5848447</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, PySpark, PostgreSQL, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25fb588ea8f37c03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, S3, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebadd001a801356b</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Lake, Docker, CI/CD, Jenkins, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a038d39055bc1489</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SAP Security Administrator</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=752638bb6e37ae1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Junior Cloud Security Analyst</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ebf1dcce2f9d82c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Junior DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58b91e8125ba691e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CrowdStrike Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49a243fe1986b84</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst 1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chegg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cbe3791ed36a509</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-31.xlsx
+++ b/daily_matches/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AmeriSave Mortgage</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Mistral, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feae9ccbf61bd2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, NoSQL, Tableau</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Senior Advisor II, AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, Docker, Git, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
+          <t>https://www.indeed.com/viewjob?jk=8a97799b41a10028</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Redshift, Kinesis, Git, Redshift, Tableau, Quicksight, Python</t>
+          <t>RAG, AWS SageMaker, S3, Glue, Redshift, Kinesis, CI/CD, GitHub Actions, Git, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Solution Architect - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gibsonia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Python</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfca1a7e8222a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3a33fce24522f7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer - Generative AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=12a7bc190503f03a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack, UI</t>
+          <t>Data Analytics Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Berkshire Grey</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, GCP Vertex AI, Data Lake, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707fd9c7800d5d83</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc48fc16ac9e795</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Sr Engineer, Machine Learning Engineering (ML Apps)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d600b4b70cf41eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - Generative AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C3 AI</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, LLaMA, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ea5bf4bd279e43</t>
+          <t>https://www.indeed.com/viewjob?jk=6f7b71fdb9584241</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer - AI Department</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DesignLibro Inc</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b84ca4e1fbdedeb</t>
+          <t>https://www.indeed.com/viewjob?jk=0af3d53501db4f28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Java Developer - Virtual</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, SQL, R, Java</t>
+          <t>RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe7f12be844b73</t>
+          <t>https://www.indeed.com/viewjob?jk=dffeafefe661c10c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Workato</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Snowflake, Databricks, Python, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802245f230147718</t>
+          <t>https://www.indeed.com/viewjob?jk=1460f7b83686c7d2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, .NET / C# (AI-Augmented Development)</t>
+          <t>Bac End AI Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321b4969b5d9936f</t>
+          <t>https://www.indeed.com/viewjob?jk=120c589e14b0495d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>AI Enablement Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Kubernetes, Terraform, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baf66a3d9ea7d49</t>
+          <t>https://www.indeed.com/viewjob?jk=13dfabc6281ad00e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Hadoop, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,322 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75994c955dad2ec0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Aspen Skiing Company</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10a9414bce3bda0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Data Lake, Snowflake, BigQuery, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - PHP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Docker, Git, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8165f2f59301815</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Database Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Chess.com</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>(OP- RPD) Senior Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Reveal-Brainspace</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1083865aa8a71bef</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Clarivate</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, MySQL, MongoDB, Cassandra, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4de0fa1838e91f5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence and Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cumberland Farms</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Westborough, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, MLflow, Databricks, Python, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb94f0d6515d86e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Frontline Education</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229a5f247ca6fb58</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Shipt</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Snowflake, BigQuery, Python, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3241e5abd40b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=f681e1f246fd748a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-31.xlsx
+++ b/daily_matches/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>AI Engineer, Data Scientist, RAG, Pinecone, AWS SageMaker, S3, Kinesis, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5a21d896e67e9f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Software Engineer III - Python AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cd11ff30fc362a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Advisor II, AI/ML Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, Docker, Git, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Databricks, Matplotlib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a97799b41a10028</t>
+          <t>https://www.indeed.com/viewjob?jk=d21ea46b0cd14344</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, Glue, Redshift, Kinesis, CI/CD, GitHub Actions, Git, Redshift</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, S3, FastAPI, Docker, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd7d3804967d98b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solution Architect - Artificial Intelligence</t>
+          <t>Field Engineer - Data Integration &amp; AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gibsonia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Docker, Kubernetes, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3a33fce24522f7</t>
+          <t>https://www.indeed.com/viewjob?jk=84d683c622c98ed1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, AWS SageMaker, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a7bc190503f03a</t>
+          <t>https://www.indeed.com/viewjob?jk=64c3e5acc6e5ee6b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Intern</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, GCP Vertex AI, Data Lake, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc48fc16ac9e795</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Engineer, Machine Learning Engineering (ML Apps)</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Databricks, Kafka, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d600b4b70cf41eb</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Applied AI ML. Sr. Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, MLflow, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f7b71fdb9584241</t>
+          <t>https://www.indeed.com/viewjob?jk=415f6e457e6c44ae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Data Lake, MLflow, CI/CD, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af3d53501db4f28</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffeafefe661c10c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6d920c4c2bd57b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>IBM X-Force Intelligence Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Workato</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, CI/CD, Jenkins, Git, Tableau, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1460f7b83686c7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bd46ddab447d11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bac End AI Developer</t>
+          <t>Senior Graph Data Scientist – Identity Analytics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=120c589e14b0495d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc47fd667fe7a983</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Enablement Intern</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Kubernetes, Terraform, Git, Python, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Git, Kafka, MongoDB, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,147 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13dfabc6281ad00e</t>
+          <t>https://www.indeed.com/viewjob?jk=d58efb4b3a95f8a3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>R59622 Senior Software Engineer - AI/Computer Vision (Camera Systems)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Motorola Solutions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b645ebc38d4dd4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Supervisor, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Availity, LLC.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8549b1f5f68aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Hadoop, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f681e1f246fd748a</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, Hadoop, Python, SQL, R, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d61de93e310b73be</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, Hadoop, Python, SQL, R, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd0e33ee9759ea2b</t>
         </is>
       </c>
     </row>
